--- a/resources/one-person-ai-business/files/opab-adv-flywheel-tracker.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-flywheel-tracker.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,11 +61,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -521,7 +514,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
@@ -800,53 +792,70 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>In this model the referral line climbs as the base grows — for the SAME hours — so give-</t>
-        </is>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>…the same, in minutes (the book's 48 → 45 → 44)</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>ROUND(B17*60,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="7">
+        <f>ROUND(C17*60,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="7">
+        <f>ROUND(D17*60,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="7">
+        <f>ROUND(E17*60,0)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>first hours per paying customer FALL quarter over quarter. That decline IS the flywheel.</t>
+          <t>In this model the referral line climbs as the base grows — for the SAME hours — so give-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>If it stays flat after two quarters, your give-first work isn't shareable enough — fix that,</t>
+          <t>first hours per paying customer FALL quarter over quarter. That decline IS the flywheel.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>If it stays flat after two quarters, your give-first work isn't shareable enough — fix that,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>not the amount of posting. Owned reach is portable permission, not immunity: lists decay.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>From The One-Person AI Business — Advanced. The full method + the shelf: eports.global/one-person-ai-business</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>From The One-Person AI Business — Advanced. The full method + the shelf: eports.global/one-person-ai-business</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/one-person-ai-business/files/opab-adv-flywheel-tracker.xlsx
+++ b/resources/one-person-ai-business/files/opab-adv-flywheel-tracker.xlsx
@@ -853,7 +853,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
